--- a/КПП/Том СКС КПП/Протокол сопротивления изоляции СКС КПП (образец и бланк).xlsx
+++ b/КПП/Том СКС КПП/Протокол сопротивления изоляции СКС КПП (образец и бланк).xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бланк" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Образец'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Образец'!$17:$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Бланк'!$16:$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +21,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -71,6 +77,12 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -111,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -125,30 +137,36 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,692 +549,708 @@
     <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ООО «АльтЭн» (лицо, выполнившее работы), ОГРН 1024000944098, ИНН 4025062969</t>
+          <t>ОБРАЗЕЦ ЗАПОЛНЕНИЯ — для сверки с протоколом исполнителя измерений. Значения типичны для новых линий данного типа и длины; в действительном протоколе — только фактические показания прибора. Не подписывается и в ИД не включается.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>ООО «АльтЭн» (лицо, выполнившее работы), ОГРН 1024000944098, ИНН 4025062969</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>249035, Калужская обл., г. Обнинск, пр-т Маркса, д. 14, пом. 18</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ПРОТОКОЛ № ПИ-СКС-КПП</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>измерения сопротивления изоляции кабельных линий</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>измерения сопротивления изоляции кабельных линий</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
           <t>Дата проведения испытаний: 27.10.2026</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Объект: «Центр временного содержания иностранных граждан», Калужская область, м. р-н Боровский, д. Старомихайловское, ул. 1-я Индустриальная, вл. 2, земельный участок с кадастровым номером 40:03:068314:1874</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Здание: КПП. Система: структурированная кабельная система (СКС). Заказчик испытаний: ООО «АльтЭн», ОГРН 1024000944098, ИНН 4025062969.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Исполнительная документация: 16/1/26-СКС-ИД-КПП, лист 2; кабельный журнал 16/1/26-СКС-ИД-КПП.КЖ. Рабочая документация 16/1/26-СКС-Р.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Цель испытаний: приёмо-сдаточные испытания — проверка сопротивления изоляции смонтированных кабельных линий.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Условия испытаний: температура воздуха +20 °С, относительная влажность 55 %, атмосферное давление 745 мм рт. ст.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Нормативные документы: ГОСТ Р 50571.16-2019 (МЭК 60364-6:2016), п. 6.4.3.3; ПУЭ (7-е изд.), п. 1.8.37; СП 76.13330.2016; эксплуатационная документация изготовителей кабелей.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Нормы: цепи SELV/PELV (до 50 В: шлейфы, интерфейсы, питание 12–24 В) — испытательное напряжение 250 В, сопротивление изоляции не менее 0,5 МОм; цепи до 500 В (линии оповещения 100 В, сеть 230 В) — 500 В, не менее 1,0 МОм. Измеряется сопротивление изоляции между жилами и между жилами и землёй (ГОСТ Р 50571.16-2019, п. 6.4.3.4: для SELV — отделение от земли); для кабелей без PE-жилы — относительно экрана (F/UTP) или заземлённой конструкции (лоток, шина PE шкафа). Измерения при отключённых приборах (концы линий разведены).</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Средства измерений: Измеритель параметров электробезопасности Sonel MPI-525 (Госреестр СИ РФ № 44170-10), зав. № A92551; поверка: ФГИС «Аршин», свидетельство № С-ВВО/28-05-2026/529221088 от 28.05.2026, действительна до 27.05.2027. Режим RISO (ГОСТ IEC 61557-2): 250 В — диапазон 0,25…999 МОм; 500 В — 0,5 МОм…2,00 ГОм; измерительный ток &lt; 2 мА. Измерения выполнил: инженер Андреев М.В., III группа по электробезопасности до 1000 В.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Обозначение линии (по КЖ)</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Начало</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Конец</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Марка кабеля</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Сечение</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Длина, м</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Испыт. напряжение, В</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>R изоляции между жилами, МОм</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>R изоляции жил относительно земли (PE / экран / заземлённый лоток), МОм</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Норма, не менее, МОм</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t>Вывод</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
+    <row r="18">
+      <c r="A18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>СКС2</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>XS1.1</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Cabeus F/UTP Cat 6 LSZH</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G18" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H18" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>соответствует</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
+    <row r="19">
+      <c r="A19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>СКС3</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>XS1.2</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Cabeus F/UTP Cat 6 LSZH</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G19" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H19" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>соответствует</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
+    <row r="20">
+      <c r="A20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>СКС4</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>XS1.3</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Cabeus F/UTP Cat 6 LSZH</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G20" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H20" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>соответствует</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
+    <row r="21">
+      <c r="A21" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>СКС5</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>XS1.4</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Cabeus F/UTP Cat 6 LSZH</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H21" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="J20" s="8" t="n">
+      <c r="J21" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>соответствует</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
+    <row r="22">
+      <c r="A22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>СКС6</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>XS1.5</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Cabeus F/UTP Cat 6 LSZH</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G22" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H22" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>соответствует</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
+    <row r="23">
+      <c r="A23" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>ТФ1</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>X1.1</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>ParLan U/UTP Cat 5e 4×2×0,52 PVC</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G23" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H23" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>соответствует</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
+    <row r="24">
+      <c r="A24" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>ТФ2</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>X1.2</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>ParLan U/UTP Cat 5e 4×2×0,52 PVC</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="G24" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="H24" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>соответствует</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="n">
+    <row r="25">
+      <c r="A25" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>ТФ3</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>X1.3</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>ParLan U/UTP Cat 5e 4×2×0,52 PVC</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G25" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="8" t="n">
+      <c r="H25" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>соответствует</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Заключение: Сопротивление изоляции всех испытанных кабельных линий соответствует требованиям ГОСТ Р 50571.16-2019 и ПУЭ п. 1.8.37. Линии пригодны к эксплуатации.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Протокол распространяется только на испытанные линии. Запись «&gt; 999» / «&gt; 2,00 ГОм» — показание выше верхнего предела диапазона прибора.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Измерения выполнил</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>инженер Андреев М.В. (III группа по ЭБ до 1000 В)</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr">
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Протокол проверил</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>начальник отдела систем технической безопасности Иванчук М.В.</t>
         </is>
       </c>
-      <c r="K30" s="14" t="inlineStr">
+      <c r="K31" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Присутствовал представитель лица, осуществляющего строительство</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="K31" s="14" t="inlineStr">
+      <c r="K32" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>ОБРАЗЕЦ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
     <mergeCell ref="K30:L30"/>
     <mergeCell ref="A7:L7"/>
-    <mergeCell ref="G29:J29"/>
     <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A3:L3"/>
     <mergeCell ref="A12:L12"/>
-    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="G32:J32"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="K29:L29"/>
     <mergeCell ref="G31:J31"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="K32:L32"/>
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="K31:L31"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A4:L4"/>
     <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A28:L28"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A15:L15"/>
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A6:L6"/>
@@ -1252,570 +1286,570 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ООО «АльтЭн» (лицо, выполнившее работы), ОГРН 1024000944098, ИНН 4025062969</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>249035, Калужская обл., г. Обнинск, пр-т Маркса, д. 14, пом. 18</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ПРОТОКОЛ № ПИ-СКС-КПП</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>измерения сопротивления изоляции кабельных линий</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Дата проведения испытаний: __.__.____</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Объект: «Центр временного содержания иностранных граждан», Калужская область, м. р-н Боровский, д. Старомихайловское, ул. 1-я Индустриальная, вл. 2, земельный участок с кадастровым номером 40:03:068314:1874</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Здание: КПП. Система: структурированная кабельная система (СКС). Заказчик испытаний: ООО «АльтЭн», ОГРН 1024000944098, ИНН 4025062969.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Исполнительная документация: 16/1/26-СКС-ИД-КПП, лист 2; кабельный журнал 16/1/26-СКС-ИД-КПП.КЖ. Рабочая документация 16/1/26-СКС-Р.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Цель испытаний: приёмо-сдаточные испытания — проверка сопротивления изоляции смонтированных кабельных линий.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Условия испытаний: температура воздуха ____ °С, относительная влажность ____ %, атмосферное давление ____ мм рт. ст.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Нормативные документы: ГОСТ Р 50571.16-2019 (МЭК 60364-6:2016), п. 6.4.3.3; ПУЭ (7-е изд.), п. 1.8.37; СП 76.13330.2016; эксплуатационная документация изготовителей кабелей.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Нормы: цепи SELV/PELV (до 50 В: шлейфы, интерфейсы, питание 12–24 В) — испытательное напряжение 250 В, сопротивление изоляции не менее 0,5 МОм; цепи до 500 В (линии оповещения 100 В, сеть 230 В) — 500 В, не менее 1,0 МОм. Измеряется сопротивление изоляции между жилами и между жилами и землёй (ГОСТ Р 50571.16-2019, п. 6.4.3.4: для SELV — отделение от земли); для кабелей без PE-жилы — относительно экрана (F/UTP) или заземлённой конструкции (лоток, шина PE шкафа). Измерения при отключённых приборах (концы линий разведены).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Средства измерений: Измеритель параметров электробезопасности Sonel MPI-525 (Госреестр СИ РФ № 44170-10), зав. № A92551; поверка: ФГИС «Аршин», свидетельство № С-ВВО/28-05-2026/529221088 от 28.05.2026, действительна до 27.05.2027. Режим RISO (ГОСТ IEC 61557-2): 250 В — диапазон 0,25…999 МОм; 500 В — 0,5 МОм…2,00 ГОм; измерительный ток &lt; 2 мА. Измерения выполнил: инженер Андреев М.В., III группа по электробезопасности до 1000 В.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Обозначение линии (по КЖ)</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Начало</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Конец</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Марка кабеля</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>Сечение</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Длина, м</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Испыт. напряжение, В</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>R изоляции между жилами, МОм</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>R изоляции жил относительно земли (PE / экран / заземлённый лоток), МОм</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>Норма, не менее, МОм</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="L16" s="8" t="inlineStr">
         <is>
           <t>Вывод</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>СКС2</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>XS1.1</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Cabeus F/UTP Cat 6 LSZH</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H17" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I17" s="8" t="inlineStr"/>
-      <c r="J17" s="8" t="inlineStr"/>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr"/>
+      <c r="L17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>СКС3</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>XS1.2</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Cabeus F/UTP Cat 6 LSZH</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I18" s="8" t="inlineStr"/>
-      <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>СКС4</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>XS1.3</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Cabeus F/UTP Cat 6 LSZH</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I19" s="8" t="inlineStr"/>
-      <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr"/>
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>СКС5</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>XS1.4</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Cabeus F/UTP Cat 6 LSZH</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I20" s="8" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr"/>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>СКС6</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>XS1.5</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Cabeus F/UTP Cat 6 LSZH</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr"/>
+      <c r="J21" s="9" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr"/>
+      <c r="L21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>ТФ1</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>X1.1</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>ParLan U/UTP Cat 5e 4×2×0,52 PVC</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I22" s="8" t="inlineStr"/>
-      <c r="J22" s="8" t="inlineStr"/>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr"/>
+      <c r="J22" s="9" t="inlineStr"/>
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>ТФ2</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>X1.2</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>ParLan U/UTP Cat 5e 4×2×0,52 PVC</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="G23" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="H23" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I23" s="8" t="inlineStr"/>
-      <c r="J23" s="8" t="inlineStr"/>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr"/>
+      <c r="L23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>ТФ3</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>XR1 / патч-панель ПП1</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>X1.3</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>ParLan U/UTP Cat 5e 4×2×0,52 PVC</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>4х2x0,52</t>
         </is>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G24" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I24" s="8" t="inlineStr"/>
-      <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr"/>
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr"/>
+      <c r="L24" s="9" t="inlineStr"/>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Заключение: ______________________________________________________________________________________________</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Протокол распространяется только на испытанные линии. Запись «&gt; 999» / «&gt; 2,00 ГОм» — показание выше верхнего предела диапазона прибора.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Измерения выполнил</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>инженер Андреев М.В. (III группа по ЭБ до 1000 В)</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr">
+      <c r="K29" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Протокол проверил</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>начальник отдела систем технической безопасности Иванчук М.В.</t>
         </is>
       </c>
-      <c r="K30" s="14" t="inlineStr">
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Присутствовал представитель лица, осуществляющего строительство</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="K31" s="14" t="inlineStr">
+      <c r="K31" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>

--- a/КПП/Том СКС КПП/Протокол сопротивления изоляции СКС КПП (образец и бланк).xlsx
+++ b/КПП/Том СКС КПП/Протокол сопротивления изоляции СКС КПП (образец и бланк).xlsx
@@ -587,7 +587,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Дата проведения испытаний: 27.10.2026</t>
+          <t>Дата проведения испытаний: 24.10.2026</t>
         </is>
       </c>
     </row>
